--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2944,7 +2944,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004614</v>
+        <v>121004621</v>
       </c>
       <c r="B19" t="n">
         <v>100972</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2994,14 +2994,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullen, mellan torpgrunden och vändplan N därom, västra vägrenen, Upl</t>
+          <t>Kullen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>692417</v>
+        <v>692434</v>
       </c>
       <c r="R19" t="n">
-        <v>6654454</v>
+        <v>6654400</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Skogsbilvägren och trampad mark intill</t>
+          <t>I grus på skogsbilvägren.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004621</v>
+        <v>121004624</v>
       </c>
       <c r="B20" t="n">
         <v>100972</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3130,14 +3130,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullen, Upl</t>
+          <t>Kullen, 115 m SSO om torpgrunden, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692434</v>
+        <v>692481</v>
       </c>
       <c r="R20" t="n">
-        <v>6654400</v>
+        <v>6654362</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Totalt i området Kullen-Myra noterades 5067 ex (många mycket små) vid besöket.</t>
+          <t>Västra sidan av Myravägen, mittför avtag markväg åt öster. Totalt i området Kullen-Myra noterades 5067 ex (många mycket små) vid besöket.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>I grus på skogsbilvägren.</t>
+          <t>Skogsbilvägren invid häll</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004624</v>
+        <v>121004620</v>
       </c>
       <c r="B21" t="n">
         <v>100972</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3266,14 +3266,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullen, 115 m SSO om torpgrunden, Upl</t>
+          <t>Kullen, alldeles N om torpgrunden, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>692481</v>
+        <v>692426</v>
       </c>
       <c r="R21" t="n">
-        <v>6654362</v>
+        <v>6654403</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Västra sidan av Myravägen, mittför avtag markväg åt öster. Totalt i området Kullen-Myra noterades 5067 ex (många mycket små) vid besöket.</t>
+          <t>Totalt i området Kullen-Myra noterades 5067 ex (många mycket små) vid besöket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Skogsbilvägren invid häll</t>
+          <t>Hällmark</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3349,142 +3349,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>121004620</v>
-      </c>
-      <c r="B22" t="n">
-        <v>100972</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1449</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Hällebräcka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Saxifraga osloënsis</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Knaben</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Kullen, alldeles N om torpgrunden, Upl</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>692426</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6654403</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Ununge</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Totalt i området Kullen-Myra noterades 5067 ex (många mycket små) vid besöket.</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Hällmark</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3350,6 +3350,257 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133879622</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106174</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kullen (torpgrund S om Myra), Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>692417</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6654449</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Torpgrund</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133879630</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101963</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kullen, röse N om torpgrunden, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>692399</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6654463</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Markerad med naturvårdssnitsel. Inga körskador i samband med avverkningarna. Blommar som bäst nu. Räknad 10 ex i taget. Totalt i området Kullen-Myra noterades 747 ex hällebräcka vid besöket.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133879622</v>
       </c>
       <c r="B22" t="n">
-        <v>106174</v>
+        <v>106178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>133879630</v>
       </c>
       <c r="B23" t="n">
-        <v>101963</v>
+        <v>101967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133879622</v>
       </c>
       <c r="B22" t="n">
-        <v>106178</v>
+        <v>106180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>133879630</v>
       </c>
       <c r="B23" t="n">
-        <v>101967</v>
+        <v>101969</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133879622</v>
       </c>
       <c r="B22" t="n">
-        <v>106180</v>
+        <v>106208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>133879630</v>
       </c>
       <c r="B23" t="n">
-        <v>101969</v>
+        <v>101997</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 10876-2025 artfynd.xlsx
+++ b/artfynd/A 10876-2025 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>133879622</v>
       </c>
       <c r="B22" t="n">
-        <v>106208</v>
+        <v>106218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>133879630</v>
       </c>
       <c r="B23" t="n">
-        <v>101997</v>
+        <v>102007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
